--- a/test_samples/YJE_TATA/sample7_ref.xlsx
+++ b/test_samples/YJE_TATA/sample7_ref.xlsx
@@ -569,12 +569,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>31 Jul 2025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123808864</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>01 Aug 2025</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123809606</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04 Aug 2025</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123809806</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>05 Aug 2025</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123810809</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>02 Aug 2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123809892</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04 Aug 2025</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123810295</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>06 Aug 2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123811291</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>06 Aug 2025</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LPS0020047</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIETNAM</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>07 Aug 2025</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123811819</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>07 Aug 2025</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YJE123811823</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHINA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
